--- a/output/pdf_financials_xlsx/CMG.xlsx
+++ b/output/pdf_financials_xlsx/CMG.xlsx
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>34701.292</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>28826.173</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>41752.956</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -2650,43 +2650,43 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>72.41</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>75.342</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>63.239</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>63.719</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>54.29</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>40.505</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>49.068</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>59.66</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>63.083</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>43.884</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="35">
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>34701.292</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>28826.173</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>41752.956</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -2780,43 +2780,43 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>72.41</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>75.342</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>63.239</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>63.719</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>54.29</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>40.505</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>49.068</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>59.66</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>63.083</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>43.884</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>3.7</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="37">
@@ -3541,13 +3541,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>35527.184</v>
+        <v>825.8920000000001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>31400.639</v>
+        <v>2574.466</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>42817.474</v>
+        <v>1064.518</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>73.691</v>
+        <v>1.281</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>76.655</v>
+        <v>1.313</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -3575,28 +3575,28 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>55.989</v>
+        <v>1.699</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>42.189</v>
+        <v>1.684</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>61.411</v>
+        <v>1.751</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>68.354</v>
+        <v>1.504</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>69.387</v>
+        <v>6.304</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>48.459</v>
+        <v>4.575</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>31.576</v>
+        <v>7.476</v>
       </c>
     </row>
     <row r="49">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">

--- a/output/pdf_financials_xlsx/CMG.xlsx
+++ b/output/pdf_financials_xlsx/CMG.xlsx
@@ -7050,13 +7050,13 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>1.501</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>3.709</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>5.776</v>
       </c>
     </row>
     <row r="101">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -26924,7 +26924,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
